--- a/device-model-indicators/陀螺_指标库_20260225.xlsx
+++ b/device-model-indicators/陀螺_指标库_20260225.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="193" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="242" uniqueCount="51">
   <si>
     <t>型号 Model</t>
   </si>
@@ -1409,12 +1409,8 @@
       <c r="J36" s="0">
         <v>5</v>
       </c>
-      <c r="K36" s="0">
-        <v>-20</v>
-      </c>
-      <c r="L36" s="0">
-        <v>50</v>
-      </c>
+      <c r="K36" s="0"/>
+      <c r="L36" s="0"/>
       <c r="M36" s="0">
         <v>8</v>
       </c>
@@ -1426,27 +1422,15 @@
       <c r="B37" s="0">
         <v>0.0080000000000000002</v>
       </c>
-      <c r="C37" s="0">
-        <v>0.5</v>
-      </c>
+      <c r="C37" s="0"/>
       <c r="D37" s="0">
         <v>2.3999999999999999</v>
       </c>
-      <c r="E37" s="0">
-        <v>100</v>
-      </c>
-      <c r="F37" s="0">
-        <v>100</v>
-      </c>
-      <c r="G37" s="0">
-        <v>10</v>
-      </c>
-      <c r="H37" s="0">
-        <v>0.5</v>
-      </c>
-      <c r="I37" s="0">
-        <v>5</v>
-      </c>
+      <c r="E37" s="0"/>
+      <c r="F37" s="0"/>
+      <c r="G37" s="0"/>
+      <c r="H37" s="0"/>
+      <c r="I37" s="0"/>
       <c r="J37" s="0">
         <v>5</v>
       </c>

--- a/device-model-indicators/陀螺_指标库_20260225.xlsx
+++ b/device-model-indicators/陀螺_指标库_20260225.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="242" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="291" uniqueCount="51">
   <si>
     <t>型号 Model</t>
   </si>
@@ -480,7 +480,7 @@
         <v>0.02</v>
       </c>
       <c r="C8" s="0">
-        <v>0.14999999999999999</v>
+        <v>0.15</v>
       </c>
       <c r="D8" s="0"/>
       <c r="E8" s="0">
@@ -778,7 +778,7 @@
       </c>
       <c r="G17" s="0"/>
       <c r="H17" s="0">
-        <v>0.14999999999999999</v>
+        <v>0.15</v>
       </c>
       <c r="I17" s="0"/>
       <c r="J17" s="0"/>
@@ -805,7 +805,7 @@
       </c>
       <c r="G18" s="0"/>
       <c r="H18" s="0">
-        <v>0.14999999999999999</v>
+        <v>0.15</v>
       </c>
       <c r="I18" s="0">
         <v>1</v>
@@ -1218,7 +1218,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="0">
-        <v>0.14999999999999999</v>
+        <v>0.15</v>
       </c>
       <c r="C31" s="0">
         <v>0.29999999999999999</v>
@@ -1255,7 +1255,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="0">
-        <v>0.14999999999999999</v>
+        <v>0.15</v>
       </c>
       <c r="C32" s="0">
         <v>0.29999999999999999</v>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="G33" s="0"/>
       <c r="H33" s="0">
-        <v>0.14999999999999999</v>
+        <v>0.15</v>
       </c>
       <c r="I33" s="0">
         <v>2</v>
@@ -1383,28 +1383,28 @@
         <v>49</v>
       </c>
       <c r="B36" s="0">
-        <v>0.016</v>
+        <v>0.02</v>
       </c>
       <c r="C36" s="0">
-        <v>0.056000000000000001</v>
+        <v>0.070000000000000007</v>
       </c>
       <c r="D36" s="0">
-        <v>0.23999999999999999</v>
+        <v>0.29999999999999999</v>
       </c>
       <c r="E36" s="0">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F36" s="0">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G36" s="0">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H36" s="0">
-        <v>0.40000000000000002</v>
+        <v>0.46000000000000002</v>
       </c>
       <c r="I36" s="0">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="J36" s="0">
         <v>5</v>
@@ -1412,7 +1412,7 @@
       <c r="K36" s="0"/>
       <c r="L36" s="0"/>
       <c r="M36" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37">
@@ -1420,11 +1420,11 @@
         <v>50</v>
       </c>
       <c r="B37" s="0">
-        <v>0.0080000000000000002</v>
+        <v>0.01</v>
       </c>
       <c r="C37" s="0"/>
       <c r="D37" s="0">
-        <v>2.3999999999999999</v>
+        <v>3</v>
       </c>
       <c r="E37" s="0"/>
       <c r="F37" s="0"/>
@@ -1441,7 +1441,7 @@
         <v>50</v>
       </c>
       <c r="M37" s="0">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
